--- a/result/morris/morris_first_inf_ONLY_Signed_N256_seed2024.xlsx
+++ b/result/morris/morris_first_inf_ONLY_Signed_N256_seed2024.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,97 +453,97 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>infection__infection_condition</t>
+          <t>zoospore_alive__vpd</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>33.03927951388889</v>
+        <v>-18.61859809027779</v>
       </c>
       <c r="C2" t="n">
-        <v>33.55815972222223</v>
+        <v>23.72102864583334</v>
       </c>
       <c r="D2" t="n">
-        <v>24.31538432514473</v>
+        <v>27.4262438437129</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>mp_tmp__rh_wet_night</t>
+          <t>infection__infection_condition</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>23.54958767361111</v>
+        <v>18.75792100694445</v>
       </c>
       <c r="C3" t="n">
-        <v>26.84602864583333</v>
+        <v>21.11013454861112</v>
       </c>
       <c r="D3" t="n">
-        <v>29.04006401981955</v>
+        <v>19.95530470784132</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>zoospore_alive__vpd</t>
+          <t>dispersal__rain_min</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-22.76822916666667</v>
+        <v>13.27690972222222</v>
       </c>
       <c r="C4" t="n">
-        <v>26.19118923611111</v>
+        <v>18.60199652777778</v>
       </c>
       <c r="D4" t="n">
-        <v>26.97991644314992</v>
+        <v>28.68957385104877</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>dispersal__rain_min</t>
+          <t>thresholds__min_spores</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20.21744791666666</v>
+        <v>10.80805121527779</v>
       </c>
       <c r="C5" t="n">
-        <v>20.92838541666665</v>
+        <v>17.23969184027778</v>
       </c>
       <c r="D5" t="n">
-        <v>23.92255407924398</v>
+        <v>22.52314007730996</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>sporulation__Tmax</t>
+          <t>mp_tmp__rh_wet_night</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.4271918402777777</v>
+        <v>7.819227430555557</v>
       </c>
       <c r="C6" t="n">
-        <v>6.024848090277778</v>
+        <v>11.05468750000001</v>
       </c>
       <c r="D6" t="n">
-        <v>14.80311339144322</v>
+        <v>15.7254783097946</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>sporulation__MP_min</t>
+          <t>sporulation__Tmax</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.346028645833334</v>
+        <v>-3.057074652777776</v>
       </c>
       <c r="C7" t="n">
-        <v>4.640082465277778</v>
+        <v>9.388020833333334</v>
       </c>
       <c r="D7" t="n">
-        <v>10.05315356778253</v>
+        <v>17.01930276981646</v>
       </c>
     </row>
     <row r="8">
@@ -553,29 +553,29 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.3642578125</v>
+        <v>-1.220377604166667</v>
       </c>
       <c r="C8" t="n">
-        <v>3.901801215277778</v>
+        <v>7.928927951388892</v>
       </c>
       <c r="D8" t="n">
-        <v>10.66442561601753</v>
+        <v>19.78076201683735</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>incubation__spl_end</t>
+          <t>sporulation__Topt</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.790473090277779</v>
+        <v>-2.697808159722223</v>
       </c>
       <c r="C9" t="n">
-        <v>2.790473090277779</v>
+        <v>7.675672743055559</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3910054731436535</v>
+        <v>17.17820057691729</v>
       </c>
     </row>
     <row r="10">
@@ -585,45 +585,45 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.530707465277778</v>
+        <v>-1.306640624999999</v>
       </c>
       <c r="C10" t="n">
-        <v>2.123155381944444</v>
+        <v>3.714409722222223</v>
       </c>
       <c r="D10" t="n">
-        <v>11.35986473184447</v>
+        <v>10.5429238157472</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>deposition__rain_min</t>
+          <t>incubation__spl_end</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.032118055555555</v>
+        <v>2.796875000000002</v>
       </c>
       <c r="C11" t="n">
-        <v>2.071614583333333</v>
+        <v>2.796875000000002</v>
       </c>
       <c r="D11" t="n">
-        <v>7.294180602014545</v>
+        <v>0.3591618244892109</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>sporulation__Topt</t>
+          <t>deposition__rain_min</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.288411458333333</v>
+        <v>0.7710503472222222</v>
       </c>
       <c r="C12" t="n">
-        <v>1.953559027777777</v>
+        <v>2.000868055555556</v>
       </c>
       <c r="D12" t="n">
-        <v>9.16320236980388</v>
+        <v>9.111279985478459</v>
       </c>
     </row>
     <row r="13">
@@ -633,13 +633,29 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.7292751736111112</v>
+        <v>0.4188368055555556</v>
       </c>
       <c r="C13" t="n">
-        <v>1.73513454861111</v>
+        <v>1.986545138888889</v>
       </c>
       <c r="D13" t="n">
-        <v>5.344521924104506</v>
+        <v>7.807002834816303</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>sporulation__MP_min</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.96875</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1.819010416666667</v>
+      </c>
+      <c r="D14" t="n">
+        <v>6.533631779231174</v>
       </c>
     </row>
   </sheetData>
